--- a/artfynd/A 74005-2021 artfynd.xlsx
+++ b/artfynd/A 74005-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 74005-2021 artfynd.xlsx
+++ b/artfynd/A 74005-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101362742</v>
+        <v>101362741</v>
       </c>
       <c r="B2" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444383.9599903998</v>
+        <v>444384</v>
       </c>
       <c r="R2" t="n">
-        <v>7094782.483513337</v>
+        <v>7094782</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,19 +746,9 @@
           <t>2022-06-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101362755</v>
+        <v>101362742</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444383.9599903998</v>
+        <v>444384</v>
       </c>
       <c r="R3" t="n">
-        <v>7094782.483513337</v>
+        <v>7094782</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,19 +847,9 @@
           <t>2022-06-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,43 +877,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101362747</v>
+        <v>101362755</v>
       </c>
       <c r="B4" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444383.9599903998</v>
+        <v>444384</v>
       </c>
       <c r="R4" t="n">
-        <v>7094782.483513337</v>
+        <v>7094782</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,19 +948,9 @@
           <t>2022-06-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-06-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,53 +978,55 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101362767</v>
+        <v>101299244</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nöjdfjället, Jmt</t>
+          <t>Nöjden, Krokom, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444364.4024028718</v>
+        <v>444578</v>
       </c>
       <c r="R5" t="n">
-        <v>7094746.371122397</v>
+        <v>7094450</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1097,22 +1053,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-06-02</t>
+          <t>2022-05-31</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-06-02</t>
+          <t>2022-05-31</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,56 +1077,50 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Magnus Magnusson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Magnus Magnusson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>101362741</v>
+        <v>101362767</v>
       </c>
       <c r="B6" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444383.9599903998</v>
+        <v>444364</v>
       </c>
       <c r="R6" t="n">
-        <v>7094782.483513337</v>
+        <v>7094746</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1216,19 +1166,9 @@
           <t>2022-06-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-06-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,15 +1196,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103672936</v>
+        <v>101362747</v>
       </c>
       <c r="B7" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,16 +1225,20 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nöjden, 2,6 km V från befintligt hus, Jmt</t>
+          <t>Nöjdfjället, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444643.6316846627</v>
+        <v>444384</v>
       </c>
       <c r="R7" t="n">
-        <v>7094865.722657905</v>
+        <v>7094782</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1326,22 +1265,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,26 +1279,124 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Vid bäck i granskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>103672936</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nöjden, 2,6 km V från befintligt hus, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>444644</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7094866</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Vid bäck i granskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Ola Löfgren</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Ola Löfgren</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 74005-2021 artfynd.xlsx
+++ b/artfynd/A 74005-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101362741</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101362742</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101362755</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101299244</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101362767</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1295,6 +1325,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101362747</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1397,8 +1432,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103672936</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>